--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="O12" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>6.84</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>6.84</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.86</v>
+        <v>1.43</v>
       </c>
       <c r="O13" t="n">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.43</v>
+        <v>6.84</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.94</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.37</v>
+        <v>6.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="P16" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>6.84</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="O12" t="n">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>1.43</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>6.84</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>3.26</v>
+        <v>3.46</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="P13" t="n">
-        <v>2.37</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="O14" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>6.84</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="O12" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>6.84</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="O13" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>2.37</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.43</v>
+        <v>3.89</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>6.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>2.01</v>
       </c>
       <c r="O16" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>3.45</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.86</v>
+        <v>3.71</v>
       </c>
       <c r="O18" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.43</v>
+        <v>2.86</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5</v>
+        <v>3.26</v>
       </c>
       <c r="P12" t="n">
-        <v>6.84</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="O13" t="n">
-        <v>3.28</v>
+        <v>3.46</v>
       </c>
       <c r="P13" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.89</v>
+        <v>2.94</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>2.37</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>3.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.71</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.84</v>
+        <v>6.84</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.37</v>
+        <v>3.89</v>
       </c>
       <c r="O19" t="n">
         <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>4.37</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.63</v>
+        <v>4.37</v>
       </c>
       <c r="O13" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>1.43</v>
       </c>
       <c r="O14" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.37</v>
+        <v>6.84</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>3.89</v>
       </c>
       <c r="O17" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.43</v>
+        <v>2.94</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="P18" t="n">
-        <v>6.84</v>
+        <v>2.37</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.89</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>1.77</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.37</v>
+        <v>2.63</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P20" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>3.36</v>
+        <v>3.46</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.37</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.69</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.01</v>
+        <v>4.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.45</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.89</v>
+        <v>2.94</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>2.37</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.94</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.37</v>
+        <v>3.45</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>3.89</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>1.77</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>3.71</v>
       </c>
       <c r="O12" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>4.37</v>
       </c>
       <c r="O13" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>1.69</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.43</v>
+        <v>2.01</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>6.84</v>
+        <v>3.45</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.71</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.37</v>
+        <v>1.43</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>6.84</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>3.89</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>3.45</v>
+        <v>1.77</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.89</v>
+        <v>2.63</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P19" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.71</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.37</v>
+        <v>1.43</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.69</v>
+        <v>6.84</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.01</v>
+        <v>2.94</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P14" t="n">
-        <v>3.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>3.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>3.36</v>
       </c>
       <c r="P16" t="n">
-        <v>6.84</v>
+        <v>2.83</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.94</v>
+        <v>4.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.37</v>
+        <v>1.69</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.89</v>
+        <v>2.86</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>3.89</v>
       </c>
       <c r="O20" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.43</v>
+        <v>3.89</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>6.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="O14" t="n">
-        <v>3.28</v>
+        <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.71</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.83</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.37</v>
+        <v>3.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.86</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>6.84</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.63</v>
+        <v>4.37</v>
       </c>
       <c r="O19" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.89</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="O14" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>6.84</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>4.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.71</v>
+        <v>2.63</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.43</v>
+        <v>3.71</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>6.84</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.37</v>
+        <v>2.94</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="O15" t="n">
-        <v>3.36</v>
+        <v>3.46</v>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.37</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.63</v>
+        <v>3.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,49 +3269,49 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.71</v>
+        <v>4.37</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>3.89</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>3.45</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.89</v>
+        <v>3.71</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.43</v>
+        <v>2.94</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="P14" t="n">
-        <v>6.84</v>
+        <v>2.37</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="O15" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>4.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.43</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.71</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>6.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.37</v>
+        <v>2.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>2.83</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.89</v>
+        <v>2.94</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>2.37</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.71</v>
+        <v>2.86</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>3.89</v>
       </c>
       <c r="O14" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.37</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.37</v>
+        <v>3.71</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>3.46</v>
       </c>
       <c r="P17" t="n">
-        <v>6.84</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>6.84</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>4.37</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="P13" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.89</v>
+        <v>4.37</v>
       </c>
       <c r="O14" t="n">
         <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.01</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.71</v>
+        <v>2.01</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.63</v>
+        <v>3.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.43</v>
+        <v>3.89</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>6.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>3.36</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.83</v>
+        <v>6.84</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.37</v>
+        <v>2.63</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P20" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.94</v>
+        <v>3.71</v>
       </c>
       <c r="O12" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>3.89</v>
       </c>
       <c r="O13" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.37</v>
+        <v>1.43</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>6.84</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,49 +3110,49 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.71</v>
+        <v>4.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.89</v>
+        <v>2.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>2.94</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="P19" t="n">
-        <v>6.84</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.01</v>
+        <v>4.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.45</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.37</v>
+        <v>2.86</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>2.01</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,49 +2315,49 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.71</v>
+        <v>4.37</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.89</v>
+        <v>1.43</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>6.84</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>6.84</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.37</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.86</v>
+        <v>3.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>3.89</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>3.45</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>3.46</v>
       </c>
       <c r="P13" t="n">
-        <v>6.84</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="O14" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>3.89</v>
       </c>
       <c r="O15" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>3.71</v>
       </c>
       <c r="O16" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.71</v>
+        <v>2.94</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>2.37</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>2.86</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P18" t="n">
-        <v>3.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>6.84</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.89</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.37</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.01</v>
+        <v>4.37</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>3.45</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.94</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.37</v>
+        <v>6.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O18" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>6.84</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="O12" t="n">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.01</v>
+        <v>3.71</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.45</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.37</v>
+        <v>2.86</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>2.43</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.89</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.71</v>
+        <v>3.89</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>3.46</v>
       </c>
       <c r="P17" t="n">
-        <v>6.84</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.94</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.37</v>
+        <v>6.84</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>2.01</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>4.37</v>
       </c>
       <c r="O20" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>3.28</v>
+        <v>3.46</v>
       </c>
       <c r="P12" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.71</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O14" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>6.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.43</v>
+        <v>4.37</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>6.84</v>
+        <v>1.69</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.37</v>
+        <v>3.71</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4415,16 +4415,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU25"/>
+  <dimension ref="A1:AU27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>3.89</v>
       </c>
       <c r="O13" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>4.37</v>
       </c>
       <c r="O14" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.37</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>2.01</v>
       </c>
       <c r="O15" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.89</v>
+        <v>1.43</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>6.84</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>3.71</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>6.84</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.37</v>
+        <v>2.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>2.94</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P19" t="n">
-        <v>3.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.71</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3742,68 +3742,68 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="AU21" s="3" t="n">
-        <v>46185.75</v>
+        <v>46185.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46185.79166666666</v>
+        <v>46185.75</v>
       </c>
     </row>
     <row r="23">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46185.85416666666</v>
+        <v>46185.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46185.875</v>
+        <v>46185.83333333334</v>
       </c>
     </row>
     <row r="25">
@@ -4335,156 +4335,474 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" s="3" t="n">
+        <v>46185.85416666666</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" s="3" t="n">
+        <v>46185.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Argentina Prim B Nacional</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Racing Córdoba</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Chaco For Ever</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>1.99</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>2.72</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>4.36</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="Z27" t="n">
         <v>2.3</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AA27" t="n">
         <v>2.7</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AB27" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" s="3" t="n">
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" s="3" t="n">
         <v>46185.875</v>
       </c>
     </row>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.11</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>3.71</v>
       </c>
       <c r="O12" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.89</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>3.45</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.43</v>
+        <v>3.89</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>6.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.71</v>
+        <v>2.94</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>2.37</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>6.84</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>4.36</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="O27" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>4.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4733,16 +4733,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>1.11</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.71</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.01</v>
+        <v>2.94</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P13" t="n">
-        <v>3.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.37</v>
+        <v>3.71</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>4.37</v>
       </c>
       <c r="O15" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>1.69</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.89</v>
+        <v>2.63</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.94</v>
+        <v>3.89</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.37</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="O18" t="n">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>2.01</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>6.84</v>
+        <v>3.45</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>1.43</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>6.84</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>3.89</v>
       </c>
       <c r="O12" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.94</v>
+        <v>3.71</v>
       </c>
       <c r="O13" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,49 +2633,49 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.71</v>
+        <v>4.37</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.37</v>
+        <v>2.01</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.69</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="O16" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>6.84</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.89</v>
+        <v>2.63</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O18" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>3.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>3.36</v>
       </c>
       <c r="P20" t="n">
-        <v>6.84</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.89</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.71</v>
+        <v>3.89</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.37</v>
+        <v>2.86</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>2.43</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.43</v>
+        <v>3.71</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>6.84</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="O17" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>4.37</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="O20" t="n">
-        <v>3.36</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>6.84</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
         <v>2.36</v>
@@ -3767,13 +3767,13 @@
         <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
@@ -3785,7 +3785,7 @@
         <v>6.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB21" t="n">
         <v>3.1</v>
@@ -3803,7 +3803,7 @@
         <v>1.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="O26" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="P26" t="n">
-        <v>4.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="P27" t="n">
-        <v>3.6</v>
+        <v>4.36</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4733,16 +4733,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.89</v>
+        <v>2.94</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>2.37</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.86</v>
+        <v>3.71</v>
       </c>
       <c r="O14" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="O15" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,49 +2951,49 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.71</v>
+        <v>4.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.01</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.45</v>
+        <v>6.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.94</v>
+        <v>3.89</v>
       </c>
       <c r="O18" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.37</v>
+        <v>1.77</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.37</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>3.46</v>
       </c>
       <c r="P20" t="n">
-        <v>6.84</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>3.36</v>
+        <v>3.46</v>
       </c>
       <c r="P12" t="n">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="P13" t="n">
-        <v>2.37</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.37</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>2.86</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>3.26</v>
       </c>
       <c r="P17" t="n">
-        <v>6.84</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>6.84</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.63</v>
+        <v>4.37</v>
       </c>
       <c r="O20" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3788,7 +3788,7 @@
         <v>1.34</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AC21" t="n">
         <v>1.9</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O24" t="n">
         <v>5.2</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>4.36</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="O27" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>4.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4733,16 +4733,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="O6" t="n">
         <v>3.5</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>1.08</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>3.89</v>
       </c>
       <c r="O13" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.71</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.01</v>
+        <v>3.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>4.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.89</v>
+        <v>2.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>2.94</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="P19" t="n">
-        <v>6.84</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.37</v>
+        <v>1.43</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.69</v>
+        <v>6.84</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="O26" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="P26" t="n">
-        <v>4.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="P27" t="n">
-        <v>3.6</v>
+        <v>4.36</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4733,16 +4733,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="O3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="P3" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>1.08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.08</v>
+        <v>3.79</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P12" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,49 +2792,49 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.71</v>
+        <v>4.25</v>
       </c>
       <c r="O15" t="n">
         <v>3.5</v>
       </c>
       <c r="P15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.37</v>
+        <v>2.97</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>1.86</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="O18" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>1.3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>9.5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.43</v>
+        <v>2.85</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>3.38</v>
       </c>
       <c r="P20" t="n">
-        <v>6.84</v>
+        <v>2.27</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="O27" t="n">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="P27" t="n">
-        <v>4.36</v>
+        <v>3.8</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4733,16 +4733,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.79</v>
+        <v>1.08</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.13</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="O13" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.22</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.25</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>3.22</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.97</v>
+        <v>4.25</v>
       </c>
       <c r="O16" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.57</v>
+        <v>1.36</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.3</v>
+        <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>9.5</v>
+        <v>3.19</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3583,68 +3583,68 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="O20" t="n">
-        <v>3.38</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.27</v>
+        <v>4.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46185.65625</v>
+        <v>46185.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3742,68 +3742,68 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.57</v>
+        <v>2.57</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.72</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="O26" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P26" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="O27" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P27" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4733,16 +4733,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.08</v>
+        <v>3.79</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.79</v>
+        <v>1.08</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="O12" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.65</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.63</v>
+        <v>8.5</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>4.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.22</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.25</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>3.22</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="P17" t="n">
-        <v>1.86</v>
+        <v>3.19</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.36</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>3.54</v>
       </c>
       <c r="P18" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.13</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.19</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="O26" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P26" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="O27" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P27" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4733,16 +4733,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU27"/>
+  <dimension ref="A1:AU31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46185.52083333334</v>
+        <v>46185.5</v>
       </c>
     </row>
     <row r="7">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46185.54166666666</v>
+        <v>46185.5</v>
       </c>
     </row>
     <row r="8">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>3.03</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46185.54166666666</v>
+        <v>46185.52083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46185.58333333334</v>
+        <v>46185.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.79</v>
+        <v>1.77</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>4.05</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46185.58333333334</v>
+        <v>46185.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -2268,27 +2268,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46185.65625</v>
+        <v>46185.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>3.79</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>8.5</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46185.65625</v>
+        <v>46185.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2586,27 +2586,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46185.65625</v>
+        <v>46185.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46185.65625</v>
+        <v>46185.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="O16" t="n">
-        <v>3.12</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>3.22</v>
+        <v>8.5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.57</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>4.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46185.66666666666</v>
+        <v>46185.65625</v>
       </c>
     </row>
     <row r="21">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.57</v>
+        <v>4.25</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="AU21" s="3" t="n">
-        <v>46185.66666666666</v>
+        <v>46185.65625</v>
       </c>
     </row>
     <row r="22">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3901,17 +3901,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46185.75</v>
+        <v>46185.65625</v>
       </c>
     </row>
     <row r="23">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46185.79166666666</v>
+        <v>46185.65625</v>
       </c>
     </row>
     <row r="24">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.34</v>
+        <v>2.57</v>
       </c>
       <c r="O24" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46185.83333333334</v>
+        <v>46185.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>46185.85416666666</v>
+        <v>46185.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46185.875</v>
+        <v>46185.75</v>
       </c>
     </row>
     <row r="27">
@@ -4653,156 +4653,792 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" s="3" t="n">
+        <v>46185.79166666666</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="3" t="n">
+        <v>46185.83333333334</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="3" t="n">
+        <v>46185.85416666666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Chaco For Ever</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" s="3" t="n">
+        <v>46185.875</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Audax Italiano</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>La Serena</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="N31" t="n">
         <v>1.88</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O31" t="n">
         <v>3.35</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P31" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AB31" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" s="3" t="n">
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" s="3" t="n">
         <v>46185.875</v>
       </c>
     </row>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="O3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5</v>
+        <v>6.07</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.36</v>
+        <v>4.01</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="P16" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.13</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>3.66</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.25</v>
+        <v>2.22</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>3.14</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.12</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>3.22</v>
+        <v>8.5</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
         <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O30" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O31" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="P31" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5369,16 +5369,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.01</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.69</v>
+        <v>3.05</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.66</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>4.01</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="P20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="P21" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.65</v>
+        <v>3.66</v>
       </c>
       <c r="O23" t="n">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="P23" t="n">
-        <v>2.63</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.65</v>
+        <v>4.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.07</v>
+        <v>1.34</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>2.78</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>2.57</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.72</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AC25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5180,10 +5180,10 @@
         <v>1.85</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P30" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5339,10 +5339,10 @@
         <v>1.85</v>
       </c>
       <c r="O31" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P31" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5369,16 +5369,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.99</v>
+        <v>3.79</v>
       </c>
       <c r="O11" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.79</v>
+        <v>1.11</v>
       </c>
       <c r="O12" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.86</v>
+        <v>16</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.11</v>
+        <v>3.99</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="O16" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="P17" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>2.63</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>3.66</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.01</v>
+        <v>1.36</v>
       </c>
       <c r="O20" t="n">
-        <v>3.69</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>4.01</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="P22" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.66</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
         <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q24" t="n">
         <v>2</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O28" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="P28" t="n">
-        <v>7.2</v>
+        <v>6.79</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>4.06</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>4.01</v>
       </c>
       <c r="O17" t="n">
-        <v>3.12</v>
+        <v>3.69</v>
       </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.36</v>
+        <v>3.66</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>3.54</v>
       </c>
       <c r="P20" t="n">
-        <v>8.5</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>2.21</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.01</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.69</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
         <v>3.6</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>2.67</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.72</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB25" t="n">
         <v>3.1</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5180,10 +5180,10 @@
         <v>1.85</v>
       </c>
       <c r="O30" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5339,10 +5339,10 @@
         <v>1.85</v>
       </c>
       <c r="O31" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P31" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5369,16 +5369,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU31"/>
+  <dimension ref="A1:AU30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.99</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>3.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>7.4</v>
+        <v>3.05</v>
       </c>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>3.35</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>4.01</v>
       </c>
       <c r="O16" t="n">
-        <v>3.12</v>
+        <v>3.69</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.01</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
-        <v>3.69</v>
+        <v>3.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O18" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.66</v>
+        <v>1.36</v>
       </c>
       <c r="O20" t="n">
-        <v>3.54</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>8.5</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>8.5</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>3.66</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.67</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB24" t="n">
         <v>3.1</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>2.67</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.72</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AC25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5280,165 +5280,6 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46185.875</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46185</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Racing Córdoba</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Chaco For Ever</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" s="3" t="n">
         <v>46185.875</v>
       </c>
     </row>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="O6" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>3.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.99</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.01</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
-        <v>3.69</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>4.01</v>
       </c>
       <c r="O17" t="n">
-        <v>3.35</v>
+        <v>3.69</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>3.66</v>
       </c>
       <c r="O19" t="n">
-        <v>3.22</v>
+        <v>3.54</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>8.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.12</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="O3" t="n">
         <v>4.4</v>
       </c>
       <c r="P3" t="n">
-        <v>6.07</v>
+        <v>6.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA3" t="n">
         <v>1.53</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>7.4</v>
+        <v>3.05</v>
       </c>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="O12" t="n">
-        <v>3.05</v>
+        <v>7.4</v>
       </c>
       <c r="P12" t="n">
-        <v>3.35</v>
+        <v>16</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.99</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>3.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>2.88</v>
       </c>
       <c r="O16" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.01</v>
+        <v>1.36</v>
       </c>
       <c r="O17" t="n">
-        <v>3.69</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>4.01</v>
       </c>
       <c r="O18" t="n">
-        <v>3.22</v>
+        <v>3.69</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.88</v>
+        <v>3.66</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.21</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>8.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,49 +3905,49 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.15</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>2.67</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.72</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.67</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB25" t="n">
         <v>3.1</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="O8" t="n">
         <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.01</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.69</v>
+        <v>3.22</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>2.21</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.66</v>
+        <v>4.01</v>
       </c>
       <c r="O20" t="n">
-        <v>3.54</v>
+        <v>3.69</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.21</v>
+        <v>3.66</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4394,7 +4394,7 @@
         <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="S25" t="n">
         <v>1.22</v>
@@ -4403,7 +4403,7 @@
         <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V25" t="n">
         <v>1.72</v>
@@ -4418,28 +4418,28 @@
         <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>1.11</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O28" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P28" t="n">
-        <v>6.79</v>
+        <v>7.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.79</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="R2" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.36</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.34</v>
       </c>
       <c r="W2" t="n">
         <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC2" t="n">
         <v>3.14</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.93</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.21</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA3" t="n">
         <v>1.47</v>
       </c>
-      <c r="O3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="AB3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.11</v>
       </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK3" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="O4" t="n">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>1.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>5.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2165,55 +2165,55 @@
         <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>3.98</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="O13" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>3.35</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.99</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>15</v>
+        <v>4.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.2</v>
       </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AK15" t="n">
-        <v>5.4</v>
+        <v>1.59</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.88</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.36</v>
-      </c>
-      <c r="O17" t="n">
-        <v>5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>1.32</v>
       </c>
       <c r="O18" t="n">
-        <v>3.22</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.21</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.01</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3755,55 +3755,55 @@
         <v>1.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB21" t="n">
         <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3908,61 +3908,61 @@
         <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="P22" t="n">
         <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4067,61 +4067,61 @@
         <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.67</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.07</v>
+        <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>2.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>2.67</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="U25" t="n">
-        <v>1.95</v>
+        <v>3.02</v>
       </c>
       <c r="V25" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.25</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.31</v>
+        <v>2.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.86</v>
+        <v>3.52</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.62</v>
+        <v>1.81</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.33</v>
+        <v>1.41</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P30" t="n">
         <v>3.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
         <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>3.8</v>
+        <v>2.47</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.02</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>3.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.11</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="S5" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="U5" t="n">
-        <v>2.47</v>
+        <v>3.6</v>
       </c>
       <c r="V5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.44</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z5" t="n">
-        <v>3.88</v>
+        <v>2.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.73</v>
+        <v>2.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,58 +1361,58 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.25</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.91</v>
       </c>
       <c r="S6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.45</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
         <v>2.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
         <v>2.1</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.98</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC12" t="n">
         <v>4</v>
       </c>
-      <c r="R12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.47</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.68</v>
+        <v>1.82</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.2</v>
+        <v>2.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.4</v>
+        <v>2.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.88</v>
+        <v>1.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.98</v>
+        <v>5.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.68</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>5.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="R14" t="n">
-        <v>1.82</v>
+        <v>2.68</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.55</v>
+        <v>5.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.55</v>
+        <v>1.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.68</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.53</v>
+        <v>5.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.78</v>
+        <v>3.98</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="P15" t="n">
-        <v>4.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="S15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>1.54</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.59</v>
+        <v>1.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2954,62 +2954,62 @@
         <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.66</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" t="n">
         <v>1.57</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.32</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>3.42</v>
       </c>
       <c r="P18" t="n">
-        <v>8.050000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
         <v>1.36</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U18" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.04</v>
+        <v>1.16</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.51</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="S19" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96</v>
+        <v>3.28</v>
       </c>
       <c r="U19" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>4.51</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T20" t="n">
-        <v>3.28</v>
+        <v>2.96</v>
       </c>
       <c r="U20" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.09</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AF20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,58 +3905,58 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.84</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.36</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.38</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
         <v>1.75</v>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,65 +4064,65 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>1.32</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>4.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
         <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
         <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
         <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG23" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.57</v>
+        <v>3.04</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC5" t="n">
         <v>3.1</v>
       </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.26</v>
+        <v>2.06</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>5.89</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.06</v>
+        <v>1.26</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.72</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.36</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.13</v>
+        <v>1.59</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>3.98</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>1.54</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.59</v>
+        <v>1.15</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.07</v>
       </c>
-      <c r="O14" t="n">
-        <v>7</v>
-      </c>
-      <c r="P14" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>5.4</v>
+        <v>1.13</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,65 +2792,65 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.98</v>
+        <v>1.07</v>
       </c>
       <c r="O15" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AF15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.52</v>
       </c>
-      <c r="AG15" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.88</v>
+        <v>1.03</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.15</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Q16" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="V16" t="n">
         <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.01</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="O18" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>4.36</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T18" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="V18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.38</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="R19" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="U19" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="V19" t="n">
         <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>3.01</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.51</v>
+        <v>4.84</v>
       </c>
       <c r="R20" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="U20" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
         <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.36</v>
+        <v>4.51</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T21" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U21" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="V21" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4700,34 +4700,34 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="P27" t="n">
         <v>3.2</v>
       </c>
-      <c r="P27" t="n">
-        <v>3.4</v>
-      </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="V27" t="n">
         <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
         <v>1.04</v>
@@ -4739,13 +4739,13 @@
         <v>2.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.84</v>
+        <v>4.21</v>
       </c>
       <c r="AD27" t="n">
         <v>1.18</v>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="U4" t="n">
-        <v>2.47</v>
+        <v>3.6</v>
       </c>
       <c r="V4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.44</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z4" t="n">
-        <v>3.88</v>
+        <v>2.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.73</v>
+        <v>2.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>5.89</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="V5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.06</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>5.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>3.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>3.6</v>
+        <v>2.47</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.65</v>
+        <v>3.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>1.07</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.03</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.59</v>
+        <v>5.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.98</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.43</v>
+        <v>1.82</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="V12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.53</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>4.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.02</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.72</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.88</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.07</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>15</v>
+        <v>3.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.2</v>
       </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AK15" t="n">
-        <v>5.4</v>
+        <v>1.59</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>3.66</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>4.36</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T16" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
         <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,65 +3110,65 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.66</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.36</v>
+        <v>2.63</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T18" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="U18" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="V18" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.62</v>
+        <v>3.01</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,52 +3428,52 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.63</v>
+        <v>4.51</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S19" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T19" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="U19" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
         <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="AD19" t="n">
         <v>1.33</v>
@@ -3482,10 +3482,10 @@
         <v>1.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,58 +3587,58 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.84</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.36</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.38</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
         <v>1.75</v>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="P21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AG21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,58 +3905,58 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>4.84</v>
       </c>
       <c r="R22" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF22" t="n">
         <v>1.75</v>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4232,10 +4232,10 @@
         <v>4.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="S24" t="n">
         <v>1.22</v>
@@ -4259,7 +4259,7 @@
         <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="n">
         <v>1.31</v>
@@ -4271,7 +4271,7 @@
         <v>1.86</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
         <v>1.33</v>
@@ -4280,7 +4280,7 @@
         <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="O27" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q27" t="n">
         <v>2.78</v>
@@ -4718,25 +4718,25 @@
         <v>1.44</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="U27" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.05</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
         <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA27" t="n">
         <v>2.29</v>
@@ -4745,13 +4745,13 @@
         <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.21</v>
+        <v>4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
         <v>1.92</v>
@@ -4773,7 +4773,7 @@
         <v>1.32</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4871,13 +4871,13 @@
         <v>1.79</v>
       </c>
       <c r="R28" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="S28" t="n">
         <v>1.17</v>
       </c>
       <c r="T28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U28" t="n">
         <v>1.95</v>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK28" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.79</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.53</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S2" t="n">
         <v>1.33</v>
@@ -746,7 +746,7 @@
         <v>2.86</v>
       </c>
       <c r="U2" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="V2" t="n">
         <v>1.36</v>
@@ -758,19 +758,19 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="AD2" t="n">
         <v>1.34</v>
@@ -782,7 +782,7 @@
         <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,31 +884,31 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="O3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="P3" t="n">
-        <v>6.3</v>
+        <v>6.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
         <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W3" t="n">
         <v>1.12</v>
@@ -920,28 +920,28 @@
         <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>5.89</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.06</v>
+        <v>1.26</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.75</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.31</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.11</v>
@@ -1727,7 +1727,7 @@
         <v>2.59</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
         <v>1.13</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
         <v>1.3</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.47</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.68</v>
+        <v>1.82</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.2</v>
+        <v>2.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>2.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.88</v>
+        <v>1.45</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.98</v>
+        <v>5.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.68</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>5.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="O12" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="R12" t="n">
-        <v>1.82</v>
+        <v>2.68</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.45</v>
+        <v>2.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.53</v>
+        <v>5.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2483,22 +2483,22 @@
         <v>1.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.72</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
         <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
@@ -2507,16 +2507,16 @@
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
         <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
         <v>3.2</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
         <v>1.13</v>
@@ -2951,22 +2951,22 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="S16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
         <v>3.02</v>
@@ -2975,7 +2975,7 @@
         <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.08</v>
@@ -2984,31 +2984,31 @@
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD16" t="n">
         <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3119,19 +3119,19 @@
         <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="V17" t="n">
         <v>1.43</v>
@@ -3140,34 +3140,34 @@
         <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
         <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
         <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,34 +3269,34 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.63</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="U18" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -3305,29 +3305,29 @@
         <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC18" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3.7</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.51</v>
-      </c>
       <c r="R19" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="S19" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.06</v>
       </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3590,77 +3590,77 @@
         <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R20" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.36</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>3.82</v>
       </c>
       <c r="O21" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.95</v>
       </c>
-      <c r="S21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>1.32</v>
       </c>
       <c r="O22" t="n">
-        <v>3.42</v>
+        <v>4.55</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.84</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
         <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.05</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AA22" t="n">
         <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.16</v>
+        <v>3</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.32</v>
+        <v>2.08</v>
       </c>
       <c r="O23" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>8.050000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="S23" t="n">
         <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U23" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.06</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.75</v>
+        <v>3.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>3.04</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>2.47</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R24" t="n">
         <v>2.05</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.22</v>
       </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.67</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>4.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S25" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T25" t="n">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="V25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.33</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.81</v>
+        <v>2.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.41</v>
+        <v>2.33</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="O27" t="n">
         <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R27" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S27" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="U27" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
         <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4859,16 +4859,16 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O28" t="n">
         <v>4.8</v>
       </c>
       <c r="P28" t="n">
-        <v>7.16</v>
+        <v>6</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="R28" t="n">
         <v>2.56</v>
@@ -4877,13 +4877,13 @@
         <v>1.17</v>
       </c>
       <c r="T28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U28" t="n">
         <v>1.95</v>
       </c>
       <c r="V28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="W28" t="n">
         <v>1.23</v>
@@ -4898,10 +4898,10 @@
         <v>6.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AC28" t="n">
         <v>1.85</v>
@@ -4913,7 +4913,7 @@
         <v>1.33</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG28" t="n">
         <v>2.36</v>
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P30" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="R30" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="S30" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T30" t="n">
         <v>2.95</v>
       </c>
       <c r="U30" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF30" t="n">
         <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="S5" t="n">
         <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
         <v>3.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
@@ -1235,16 +1235,16 @@
         <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC5" t="n">
         <v>5.5</v>
@@ -1256,10 +1256,10 @@
         <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T6" t="n">
         <v>3</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.55</v>
-      </c>
       <c r="U6" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.67</v>
+        <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.26</v>
+        <v>2.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>5.89</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>3.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.29</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.02</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.07</v>
+        <v>2.25</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.46</v>
+        <v>3.08</v>
       </c>
       <c r="R12" t="n">
-        <v>2.68</v>
+        <v>1.82</v>
       </c>
       <c r="S12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.2</v>
       </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AK12" t="n">
-        <v>5.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>1.07</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>24</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>1.46</v>
       </c>
       <c r="R13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.1</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>2.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.13</v>
+        <v>5.4</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2792,46 +2792,46 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
         <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
         <v>1.57</v>
@@ -2843,13 +2843,13 @@
         <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.27</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="S16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.3</v>
       </c>
-      <c r="T16" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.83</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>2.63</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
         <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>3.82</v>
       </c>
       <c r="O19" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.02</v>
-      </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="U19" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>1.59</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>2.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
         <v>1.09</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK20" t="n">
         <v>1.62</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
         <v>4</v>
       </c>
-      <c r="R21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="AA21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.19</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.32</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>4.55</v>
+        <v>3.45</v>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>4.84</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="AK22" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>3</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.08</v>
+        <v>1.32</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>7.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
         <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="V23" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>3.38</v>
       </c>
       <c r="V4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.5</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AC4" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.24</v>
+        <v>1.72</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.75</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AD5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.11</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.35</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="P7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.55</v>
-      </c>
       <c r="U7" t="n">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.36</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.39</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.13</v>
+        <v>1.59</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.25</v>
+        <v>1.07</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.08</v>
+        <v>1.46</v>
       </c>
       <c r="R12" t="n">
-        <v>1.82</v>
+        <v>2.68</v>
       </c>
       <c r="S12" t="n">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>3.68</v>
+        <v>2.13</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.6</v>
+        <v>1.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>2.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.69</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.01</v>
       </c>
-      <c r="AF12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.49</v>
+        <v>5.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.07</v>
+        <v>3.98</v>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>3.65</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.46</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.18</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.42</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AK13" t="n">
-        <v>5.4</v>
+        <v>1.15</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.88</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="S15" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.9</v>
+        <v>3.68</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AE15" t="n">
         <v>1.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="R16" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,65 +3110,65 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.63</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.82</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="P19" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.59</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.21</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.43</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>1.32</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
         <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>2.08</v>
       </c>
       <c r="O22" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.84</v>
+        <v>2.75</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="U22" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.17</v>
+        <v>3.46</v>
       </c>
       <c r="AD22" t="n">
         <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF22" t="n">
         <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.32</v>
+        <v>2.75</v>
       </c>
       <c r="O23" t="n">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>7.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.8</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S23" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="AK23" t="n">
-        <v>3</v>
+        <v>1.41</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.47</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>4.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S24" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T24" t="n">
-        <v>2.53</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>2.82</v>
+        <v>1.95</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.99</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.01</v>
+        <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.69</v>
+        <v>3.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,65 +4382,65 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>2.47</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.74</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R25" t="n">
         <v>2.05</v>
       </c>
-      <c r="R25" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.22</v>
       </c>
-      <c r="T25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD25" t="n">
+      <c r="AE25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.9</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="U2" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V2" t="n">
         <v>1.36</v>
@@ -770,19 +770,19 @@
         <v>1.79</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
         <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,31 +884,31 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="P3" t="n">
-        <v>6.71</v>
+        <v>6.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
         <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
         <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
         <v>1.12</v>
@@ -923,25 +923,25 @@
         <v>4.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AB3" t="n">
         <v>2.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
         <v>2.25</v>
@@ -1220,13 +1220,13 @@
         <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
         <v>1.07</v>
@@ -1241,25 +1241,25 @@
         <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="P6" t="n">
-        <v>5.89</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3.72</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="S6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.35</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.75</v>
       </c>
-      <c r="O7" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.8</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.37</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
         <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.64</v>
+        <v>3.96</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="P9" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="U11" t="n">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.17</v>
+        <v>1.54</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.88</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.07</v>
+        <v>2.25</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.46</v>
+        <v>3.08</v>
       </c>
       <c r="R12" t="n">
-        <v>2.68</v>
+        <v>1.82</v>
       </c>
       <c r="S12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.2</v>
       </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AK12" t="n">
-        <v>5.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="O13" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.88</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>1.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T14" t="n">
         <v>4.4</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U14" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.13</v>
+        <v>6.35</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="S15" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>3.68</v>
+        <v>2.9</v>
       </c>
       <c r="V15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.2</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.1</v>
       </c>
       <c r="AE15" t="n">
         <v>1.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.15</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Q16" t="n">
-        <v>2.63</v>
+        <v>3.36</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S16" t="n">
         <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.27</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="S17" t="n">
         <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF17" t="n">
         <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>2.89</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.17</v>
+        <v>3.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
         <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>1.33</v>
       </c>
       <c r="O19" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W19" t="n">
         <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.32</v>
       </c>
-      <c r="O20" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="P20" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="Z20" t="n">
         <v>2.88</v>
       </c>
-      <c r="U20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>3.93</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK20" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>4.79</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.25</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z21" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.43</v>
+        <v>3.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.75</v>
+        <v>4.26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="S22" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T22" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="U22" t="n">
-        <v>2.97</v>
+        <v>2.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.08</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.46</v>
+        <v>2.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,55 +4064,55 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>3.67</v>
       </c>
       <c r="O23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.4</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U23" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="n">
         <v>1.18</v>
@@ -4121,7 +4121,7 @@
         <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>4.74</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S24" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="U24" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5</v>
+        <v>2.99</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.31</v>
+        <v>2.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.86</v>
+        <v>3.8</v>
       </c>
       <c r="AD24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.9</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>2.33</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.47</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S25" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T25" t="n">
-        <v>2.53</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>2.82</v>
+        <v>1.95</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.99</v>
+        <v>6.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.01</v>
+        <v>1.31</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.69</v>
+        <v>2.92</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.84</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
         <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>1.4</v>
@@ -4727,7 +4727,7 @@
         <v>1.33</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
         <v>1.05</v>
@@ -4736,7 +4736,7 @@
         <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA27" t="n">
         <v>2.28</v>
@@ -4754,7 +4754,7 @@
         <v>1.04</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
         <v>1.83</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK27" t="n">
         <v>1.65</v>
@@ -4901,7 +4901,7 @@
         <v>1.31</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AC28" t="n">
         <v>1.85</v>
@@ -4913,10 +4913,10 @@
         <v>1.33</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5177,19 +5177,19 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="S30" t="n">
         <v>1.3</v>
@@ -5219,7 +5219,7 @@
         <v>1.74</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC30" t="n">
         <v>2.69</v>
@@ -5234,7 +5234,7 @@
         <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.55</v>
-      </c>
       <c r="U4" t="n">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.29</v>
+        <v>2.06</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.46</v>
+        <v>3.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.07</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>2.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AK5" t="n">
         <v>1.4</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>2.11</v>
       </c>
       <c r="O6" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.72</v>
+        <v>2.88</v>
       </c>
       <c r="R6" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S6" t="n">
         <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.51</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>5.73</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.4</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.06</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="P10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.25</v>
+        <v>3.38</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.08</v>
+        <v>4.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.02</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.38</v>
+        <v>1.05</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T13" t="n">
         <v>4.4</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U13" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.19</v>
+        <v>6.35</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.05</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>8.5</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>3.25</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.36</v>
       </c>
-      <c r="R14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AK14" t="n">
-        <v>6.35</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P15" t="n">
         <v>3.1</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.2</v>
-      </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="S15" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="U15" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.3</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.7</v>
+        <v>2.89</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="AC17" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.2</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U18" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.89</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.62</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.57</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.79</v>
+        <v>2.62</v>
       </c>
       <c r="R21" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="U21" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
         <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.26</v>
+        <v>4.79</v>
       </c>
       <c r="R22" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
         <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>3.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.11</v>
+        <v>2.48</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.88</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="P7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.12</v>
-      </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.94</v>
+        <v>2.36</v>
       </c>
       <c r="AA7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.43</v>
+        <v>1.82</v>
       </c>
       <c r="S11" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>3.28</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
-        <v>2.34</v>
+        <v>3.58</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.1</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.54</v>
+        <v>2.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>1.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>5.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>8.5</v>
+        <v>3.38</v>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.36</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>3.15</v>
+        <v>2.43</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T13" t="n">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="U13" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.02</v>
+        <v>1.88</v>
       </c>
       <c r="AK13" t="n">
-        <v>6.35</v>
+        <v>1.19</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>8.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.25</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.22</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7</v>
+        <v>3.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.45</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.44</v>
+        <v>2.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.89</v>
       </c>
       <c r="AE14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.02</v>
       </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>6.35</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
         <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R15" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.02</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.26</v>
+        <v>3.36</v>
       </c>
       <c r="R16" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="S16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.33</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.19</v>
+        <v>7.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
         <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="S18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.3</v>
       </c>
-      <c r="T18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.33</v>
+        <v>2.89</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.6</v>
+        <v>3.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.57</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,65 +3428,65 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P19" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="R19" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U19" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG19" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.09</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.75</v>
+        <v>4.26</v>
       </c>
       <c r="R20" t="n">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="S20" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>3.02</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC20" t="n">
-        <v>3.93</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.62</v>
+        <v>4.79</v>
       </c>
       <c r="R21" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="U21" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
         <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="O22" t="n">
         <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.79</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T22" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.19</v>
+        <v>2.66</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.67</v>
+        <v>2.09</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="S23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.31</v>
       </c>
-      <c r="T23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.45</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.66</v>
+        <v>3.93</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.51</v>
+        <v>2.64</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>2.73</v>
       </c>
       <c r="P4" t="n">
-        <v>5.73</v>
+        <v>2.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="S4" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>3.76</v>
       </c>
       <c r="V4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.06</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="U5" t="n">
-        <v>3.76</v>
+        <v>2.48</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.24</v>
+        <v>3.94</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.12</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.94</v>
+        <v>2.36</v>
       </c>
       <c r="AA6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.11</v>
+        <v>1.51</v>
       </c>
       <c r="O7" t="n">
-        <v>2.89</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z7" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.25</v>
       </c>
-      <c r="O11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.38</v>
+        <v>1.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T12" t="n">
         <v>4.4</v>
       </c>
-      <c r="R12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U12" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.19</v>
+        <v>6.35</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="O13" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.1</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.88</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
         <v>1.19</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.05</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>8.5</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="T14" t="n">
-        <v>4.4</v>
+        <v>2.24</v>
       </c>
       <c r="U14" t="n">
-        <v>1.95</v>
+        <v>3.58</v>
       </c>
       <c r="V14" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.1</v>
       </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.48</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>6.35</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R16" t="n">
         <v>2.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.26</v>
       </c>
       <c r="S16" t="n">
         <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.09</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>7.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.75</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>1.41</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>4.26</v>
       </c>
       <c r="R19" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
         <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
         <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="O20" t="n">
         <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.26</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
         <v>1.31</v>
       </c>
       <c r="T20" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,65 +3746,65 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.79</v>
+        <v>2.75</v>
       </c>
       <c r="R21" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="U21" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.08</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AF21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.87</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>4.79</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="V22" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.66</v>
+        <v>3.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.09</v>
+        <v>1.33</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>7.5</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.75</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK23" t="n">
         <v>3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S24" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="T24" t="n">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="V24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.33</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,80 +4382,80 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="U25" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="V25" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.25</v>
+        <v>2.99</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.31</v>
+        <v>2.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.86</v>
+        <v>3.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AF25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK25" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.3</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
         <v>3.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -4736,22 +4736,22 @@
         <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
         <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
         <v>1.9</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.64</v>
+        <v>1.51</v>
       </c>
       <c r="O4" t="n">
-        <v>2.73</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.74</v>
+        <v>5.73</v>
       </c>
       <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3.4</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AA4" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.51</v>
+        <v>2.64</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>2.73</v>
       </c>
       <c r="P7" t="n">
-        <v>5.73</v>
+        <v>2.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>3.76</v>
       </c>
       <c r="V7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="R8" t="n">
         <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T8" t="n">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
@@ -1715,10 +1715,10 @@
         <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
         <v>1.95</v>
@@ -1730,13 +1730,13 @@
         <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
         <v>1.26</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="P9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
         <v>4.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.43</v>
+        <v>1.82</v>
       </c>
       <c r="S11" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>3.28</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
-        <v>2.34</v>
+        <v>3.58</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.1</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.54</v>
+        <v>2.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>1.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>5.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>8.5</v>
+        <v>3.38</v>
       </c>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.36</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>3.15</v>
+        <v>2.43</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T12" t="n">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.02</v>
+        <v>1.88</v>
       </c>
       <c r="AK12" t="n">
-        <v>6.35</v>
+        <v>1.19</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
         <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.02</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>1.12</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>8.5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.25</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.22</v>
+        <v>1.37</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7</v>
+        <v>3.12</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="U15" t="n">
-        <v>3.4</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.45</v>
+        <v>6.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.44</v>
+        <v>2.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.13</v>
+        <v>1.81</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.54</v>
+        <v>6.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.15</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>3.36</v>
       </c>
       <c r="R16" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S16" t="n">
         <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,55 +3110,55 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>3.67</v>
       </c>
       <c r="O17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.4</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U17" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="n">
         <v>1.18</v>
@@ -3167,7 +3167,7 @@
         <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>1.33</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19</v>
+        <v>7.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
         <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.26</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="S19" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T19" t="n">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.95</v>
+        <v>2.89</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>3.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.67</v>
+        <v>2.09</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="S20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.31</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.45</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.66</v>
+        <v>3.93</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.09</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>4.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="V21" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AF21" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC21" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.79</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
         <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>7.5</v>
+        <v>1.82</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.75</v>
+        <v>4.26</v>
       </c>
       <c r="R23" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="S23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q24" t="n">
         <v>2.05</v>
@@ -4256,7 +4256,7 @@
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z24" t="n">
         <v>6.25</v>
@@ -4265,7 +4265,7 @@
         <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC24" t="n">
         <v>1.86</v>
@@ -4280,7 +4280,7 @@
         <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
         <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="P27" t="n">
         <v>3.1</v>
@@ -4718,13 +4718,13 @@
         <v>1.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W27" t="n">
         <v>1.03</v>
@@ -4742,7 +4742,7 @@
         <v>2.19</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC27" t="n">
         <v>3.8</v>
@@ -4871,7 +4871,7 @@
         <v>1.73</v>
       </c>
       <c r="R28" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="S28" t="n">
         <v>1.17</v>
@@ -4886,7 +4886,7 @@
         <v>1.85</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
@@ -4901,13 +4901,13 @@
         <v>1.31</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC28" t="n">
         <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE28" t="n">
         <v>1.33</v>
@@ -4932,7 +4932,7 @@
         <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.04</v>
@@ -761,13 +761,13 @@
         <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.14</v>
@@ -798,7 +798,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="P3" t="n">
         <v>6.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
         <v>2.5</v>
@@ -902,7 +902,7 @@
         <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
         <v>2.02</v>
@@ -923,25 +923,25 @@
         <v>4.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="AD3" t="n">
         <v>1.58</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>5.73</v>
+        <v>5.98</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -1061,7 +1061,7 @@
         <v>1.35</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="U4" t="n">
         <v>2.75</v>
@@ -1076,10 +1076,10 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA4" t="n">
         <v>1.88</v>
@@ -1091,10 +1091,10 @@
         <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
         <v>1.85</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
         <v>2.06</v>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
         <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
         <v>2.25</v>
@@ -1223,7 +1223,7 @@
         <v>3.12</v>
       </c>
       <c r="U5" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
         <v>1.45</v>
@@ -1238,7 +1238,7 @@
         <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AA5" t="n">
         <v>1.65</v>
@@ -1253,7 +1253,7 @@
         <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF5" t="n">
         <v>1.54</v>
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R6" t="n">
         <v>1.83</v>
@@ -1379,13 +1379,13 @@
         <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
         <v>3.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
@@ -1394,10 +1394,10 @@
         <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AA6" t="n">
         <v>2.52</v>
@@ -1415,10 +1415,10 @@
         <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="P7" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
         <v>1.5</v>
@@ -1541,43 +1541,43 @@
         <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AB7" t="n">
         <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="P9" t="n">
         <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="O10" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="P10" t="n">
         <v>4.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>2.24</v>
+        <v>2.97</v>
       </c>
       <c r="U11" t="n">
-        <v>3.58</v>
+        <v>2.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>3.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.2</v>
+        <v>2.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.15</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="O12" t="n">
-        <v>3.38</v>
+        <v>8.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>1.37</v>
       </c>
       <c r="R12" t="n">
-        <v>2.43</v>
+        <v>3.12</v>
       </c>
       <c r="S12" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="U12" t="n">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.19</v>
+        <v>6.15</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.38</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U13" t="n">
         <v>3.3</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.55</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="P14" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.12</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.37</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.94</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.22</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>6.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.67</v>
+        <v>2.97</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S17" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>3.19</v>
       </c>
       <c r="V17" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>2.89</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.69</v>
+        <v>2.13</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.66</v>
+        <v>3.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AF17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.33</v>
+        <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG18" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AK18" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>3.67</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>1.69</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>2.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.62</v>
+        <v>2.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.09</v>
+        <v>1.33</v>
       </c>
       <c r="O20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK20" t="n">
         <v>3.1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.79</v>
+        <v>3.36</v>
       </c>
       <c r="R21" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="U21" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="V21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.16</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.62</v>
+        <v>4.84</v>
       </c>
       <c r="R22" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.82</v>
+        <v>3.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.26</v>
+        <v>2.76</v>
       </c>
       <c r="R23" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="S23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.31</v>
       </c>
-      <c r="T23" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.46</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.85</v>
+        <v>4.01</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.55</v>
+        <v>2.63</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="S24" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="U24" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>2.33</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="O25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB25" t="n">
         <v>3.1</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="AC25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.33</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5177,34 +5177,34 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P30" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="Q30" t="n">
         <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S30" t="n">
         <v>1.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V30" t="n">
         <v>1.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
@@ -5213,19 +5213,19 @@
         <v>1.19</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.8</v>
+        <v>4.19</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
         <v>2.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE30" t="n">
         <v>1.11</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.5</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.35</v>
-      </c>
       <c r="T4" t="n">
-        <v>2.79</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.42</v>
+        <v>2.39</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.88</v>
+        <v>2.52</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.06</v>
+        <v>1.59</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P6" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
         <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62</v>
+        <v>3.74</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>5.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="U7" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.01</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>3.42</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="P9" t="n">
         <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
         <v>4.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.12</v>
+        <v>2.87</v>
       </c>
       <c r="O12" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.37</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>3.12</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>4.4</v>
+        <v>2.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.3</v>
+        <v>3.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AK12" t="n">
-        <v>6.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="R13" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
         <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
         <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="R14" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="U14" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AC14" t="n">
         <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
         <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>1.12</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T15" t="n">
         <v>4.4</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U15" t="n">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.9</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.74</v>
+        <v>2.29</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.94</v>
+        <v>1.51</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.22</v>
+        <v>6.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.2</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.87</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="Q17" t="n">
         <v>3.6</v>
@@ -3128,46 +3128,46 @@
         <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="V17" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
         <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
         <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AB17" t="n">
         <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.62</v>
+        <v>3.82</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
         <v>1.03</v>
       </c>
       <c r="AF17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>4.27</v>
       </c>
       <c r="R18" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF18" t="n">
         <v>1.65</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.67</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>3.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="S19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.31</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.62</v>
+        <v>4.01</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.18</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,65 +3587,65 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="U20" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG20" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,31 +3746,31 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>3.67</v>
       </c>
       <c r="O21" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T21" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.11</v>
@@ -3779,31 +3779,31 @@
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>1.33</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>4.55</v>
       </c>
       <c r="P22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q22" t="n">
-        <v>4.84</v>
-      </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T22" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="V22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.4</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.16</v>
+        <v>3</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>2.69</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="P23" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.98</v>
+        <v>2.27</v>
       </c>
       <c r="S23" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="T23" t="n">
-        <v>2.53</v>
+        <v>3.28</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.95</v>
+        <v>4.71</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.01</v>
+        <v>2.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,31 +4223,31 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
         <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="S24" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T24" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="U24" t="n">
         <v>2.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
@@ -4262,13 +4262,13 @@
         <v>2.99</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="n">
         <v>1.25</v>
@@ -4277,10 +4277,10 @@
         <v>1.08</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AK24" t="n">
         <v>1.4</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -702,26 +702,26 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -734,10 +734,10 @@
         <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S2" t="n">
         <v>1.35</v>
@@ -761,13 +761,13 @@
         <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC2" t="n">
         <v>3.14</v>
@@ -779,23 +779,23 @@
         <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG2" t="n">
         <v>2.06</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AK2" t="n">
         <v>1.2</v>
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46185.27083333334</v>
@@ -880,20 +880,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
         <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P3" t="n">
         <v>6.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
         <v>2.5</v>
@@ -902,46 +902,46 @@
         <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
         <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
         <v>4.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AD3" t="n">
         <v>1.58</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,34 +957,34 @@
         <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46185.29166666666</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.62</v>
+        <v>3.74</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>5.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="U6" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.01</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>3.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S7" t="n">
         <v>1.5</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="V7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.4</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK7" t="n">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>1.12</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T11" t="n">
         <v>4.4</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>1.98</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.74</v>
+        <v>2.29</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.94</v>
+        <v>1.51</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.22</v>
+        <v>6.15</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="P12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.4</v>
       </c>
-      <c r="S12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="AA12" t="n">
         <v>2.6</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.43</v>
+        <v>5.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG12" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.77</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.12</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>3.58</v>
+        <v>2.55</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.6</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.12</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.37</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>3.12</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>4.4</v>
+        <v>2.97</v>
       </c>
       <c r="U15" t="n">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.3</v>
+        <v>3.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AK15" t="n">
-        <v>6.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.84</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.12</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="AC16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.16</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.03</v>
+        <v>1.33</v>
       </c>
       <c r="O17" t="n">
-        <v>3.12</v>
+        <v>4.55</v>
       </c>
       <c r="P17" t="n">
-        <v>2.39</v>
+        <v>7.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.4</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
         <v>3.2</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P18" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.27</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="S18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="U18" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
         <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
         <v>1.65</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="P19" t="n">
-        <v>3.16</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.76</v>
+        <v>4.84</v>
       </c>
       <c r="R19" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="S19" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.02</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="AF19" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC19" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.2</v>
+        <v>3.03</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.17</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.65</v>
+        <v>3.31</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>3.82</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>4.55</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>7.5</v>
+        <v>3.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.75</v>
+        <v>2.76</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="S22" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="T22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.55</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.07</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.75</v>
+        <v>4.01</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK22" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>4.27</v>
       </c>
       <c r="R23" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="S23" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.71</v>
+        <v>3.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
         <v>2.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R24" t="n">
         <v>2.6</v>
       </c>
-      <c r="O24" t="n">
+      <c r="S24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB24" t="n">
         <v>3.1</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>1.86</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,80 +4382,80 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG25" t="n">
         <v>2.05</v>
       </c>
-      <c r="R25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AK25" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.33</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.87</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>5.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.24</v>
+        <v>2.79</v>
       </c>
       <c r="U4" t="n">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.39</v>
+        <v>3.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.52</v>
+        <v>1.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.59</v>
+        <v>2.06</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.4</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2.25</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AG5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S6" t="n">
         <v>1.5</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.35</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.79</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.42</v>
+        <v>2.39</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.88</v>
+        <v>2.52</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.06</v>
+        <v>1.59</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.65</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AB7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="P9" t="n">
         <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="O10" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="P10" t="n">
         <v>4.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.12</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.37</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.94</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.22</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>6.15</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="U12" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
         <v>5.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
         <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="U13" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC14" t="n">
         <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
         <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>1.12</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>1.37</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="S15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.31</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.3</v>
+        <v>6.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>3.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="R16" t="n">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="T16" t="n">
-        <v>3.28</v>
+        <v>2.53</v>
       </c>
       <c r="U16" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z16" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.33</v>
+        <v>3.03</v>
       </c>
       <c r="O17" t="n">
-        <v>4.55</v>
+        <v>3.12</v>
       </c>
       <c r="P17" t="n">
-        <v>7.5</v>
+        <v>2.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S17" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.55</v>
+        <v>3.31</v>
       </c>
       <c r="V17" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>3.82</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>3.67</v>
       </c>
       <c r="O19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.03</v>
+        <v>2.69</v>
       </c>
       <c r="O20" t="n">
-        <v>3.12</v>
+        <v>3.62</v>
       </c>
       <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.39</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.31</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>4.71</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.18</v>
+        <v>1.64</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.82</v>
+        <v>2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>1.57</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>4.84</v>
       </c>
       <c r="R21" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S21" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,65 +3905,65 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG22" t="n">
         <v>2.15</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>7.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.27</v>
+        <v>1.75</v>
       </c>
       <c r="R23" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,32 +1001,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1039,111 +1039,111 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.5</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46185.5</v>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1194,115 +1194,115 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="U5" t="n">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.01</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>3.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.35</v>
+        <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.38</v>
+        <v>2.27</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46185.5</v>
@@ -1319,29 +1319,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1350,118 +1350,118 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.05</v>
       </c>
-      <c r="O6" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="AC6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.5</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46185.5</v>
@@ -1478,32 +1478,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1512,115 +1512,115 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.4</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.12</v>
-      </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.92</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.88</v>
+        <v>6.5</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46185.5</v>
@@ -1656,66 +1656,66 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.83</v>
       </c>
       <c r="U8" t="n">
         <v>2.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
         <v>1.85</v>
@@ -1724,62 +1724,62 @@
         <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
         <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '25']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46185.52083333334</v>
@@ -1815,130 +1815,130 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="O9" t="n">
         <v>3.65</v>
       </c>
       <c r="P9" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '41', '54', '90+5']</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '65', '78']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46185.54166666666</v>
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1993,111 +1993,111 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="O10" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
         <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
         <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '45+4']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
         <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46185.54166666666</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S11" t="n">
         <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U11" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>3.28</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="S12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.5</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.87</v>
+        <v>2.04</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>3.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>3.17</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="T13" t="n">
-        <v>2.97</v>
+        <v>2.13</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6</v>
+        <v>3.48</v>
       </c>
       <c r="V13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.3</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.71</v>
+        <v>6.25</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>8.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.12</v>
+        <v>1.51</v>
       </c>
       <c r="R14" t="n">
-        <v>1.82</v>
+        <v>2.89</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="T14" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>3.58</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.77</v>
       </c>
       <c r="W14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.01</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>6.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.6</v>
+        <v>1.29</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.37</v>
+        <v>3.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>1.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.46</v>
+        <v>4.3</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.12</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.37</v>
+        <v>3.39</v>
       </c>
       <c r="R15" t="n">
-        <v>3.12</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>4.4</v>
+        <v>2.76</v>
       </c>
       <c r="U15" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="V15" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.38</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.98</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.29</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>6.15</v>
+        <v>1.36</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.76</v>
+        <v>2.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.95</v>
+        <v>4.03</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
       <c r="V17" t="n">
         <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA17" t="n">
         <v>2.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AD17" t="n">
         <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AK17" t="n">
         <v>1.36</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>3.58</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>4.27</v>
       </c>
       <c r="R18" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T18" t="n">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>4.19</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
         <v>2.1</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.67</v>
+        <v>2.74</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S19" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
         <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.69</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.39</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z20" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3749,61 +3749,61 @@
         <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.84</v>
+        <v>4.95</v>
       </c>
       <c r="R21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T21" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="U21" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
         <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
         <v>1.07</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.27</v>
+        <v>3.06</v>
       </c>
       <c r="R22" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="S22" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="T22" t="n">
-        <v>3.02</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>2.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.87</v>
+        <v>4.28</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,31 +4064,31 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.55</v>
+        <v>3.52</v>
       </c>
       <c r="P23" t="n">
-        <v>7.5</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
         <v>1.07</v>
@@ -4097,47 +4097,47 @@
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK23" t="n">
-        <v>3</v>
+        <v>1.19</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4235,7 +4235,7 @@
         <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S24" t="n">
         <v>1.22</v>
@@ -4256,7 +4256,7 @@
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
         <v>6.25</v>
@@ -4382,31 +4382,31 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3.1</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R25" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S25" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T25" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="U25" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
         <v>1.03</v>
@@ -4415,19 +4415,19 @@
         <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD25" t="n">
         <v>1.25</v>
@@ -4436,10 +4436,10 @@
         <v>1.08</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4700,49 +4700,49 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O27" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S27" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
         <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
         <v>3.8</v>
@@ -4757,7 +4757,7 @@
         <v>1.9</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4865,49 +4865,49 @@
         <v>4.8</v>
       </c>
       <c r="P28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="R28" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="S28" t="n">
         <v>1.17</v>
       </c>
       <c r="T28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V28" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z28" t="n">
         <v>6.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB28" t="n">
         <v>3.1</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.83</v>
       </c>
       <c r="AE28" t="n">
         <v>1.33</v>
@@ -4916,7 +4916,7 @@
         <v>1.51</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5186,55 +5186,55 @@
         <v>3.23</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U30" t="n">
         <v>2.45</v>
       </c>
       <c r="V30" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.19</v>
+        <v>3.86</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF30" t="n">
         <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.53</v>
+        <v>2.65</v>
       </c>
       <c r="O5" t="n">
-        <v>3.8</v>
+        <v>2.44</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.48</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
         <v>3</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AS5" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="AT5" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46185.5</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,107 +1520,107 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>1.53</v>
       </c>
       <c r="O7" t="n">
-        <v>2.44</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="U7" t="n">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.01</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>3.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN7" t="n">
         <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AS7" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="AT7" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46185.5</v>
@@ -2114,149 +2114,149 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>4.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.78</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="T11" t="n">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="V11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.5</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3', '67']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.28</v>
+        <v>1.94</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46185.58333333334</v>
@@ -2273,32 +2273,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2307,115 +2307,115 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.73</v>
+        <v>2.87</v>
       </c>
       <c r="O12" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>3.78</v>
       </c>
       <c r="R12" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>2.23</v>
+        <v>3.12</v>
       </c>
       <c r="U12" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.04</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.44</v>
+        <v>3.94</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.43</v>
+        <v>1.69</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.75</v>
+        <v>2.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
         <v>1</v>
       </c>
-      <c r="AF12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-1</v>
-      </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46185.58333333334</v>
@@ -2432,32 +2432,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2466,115 +2466,115 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.04</v>
+        <v>1.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>6.25</v>
       </c>
       <c r="P13" t="n">
-        <v>3.65</v>
+        <v>8.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.17</v>
+        <v>1.51</v>
       </c>
       <c r="R13" t="n">
-        <v>1.86</v>
+        <v>2.89</v>
       </c>
       <c r="S13" t="n">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="T13" t="n">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>3.48</v>
+        <v>1.92</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.77</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.43</v>
+        <v>1.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.46</v>
+        <v>6.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>1.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '33', '34']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '74']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46185.58333333334</v>
@@ -2591,149 +2591,149 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.2</v>
+        <v>2.04</v>
       </c>
       <c r="O14" t="n">
-        <v>6.25</v>
+        <v>2.82</v>
       </c>
       <c r="P14" t="n">
-        <v>8.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.51</v>
+        <v>3.17</v>
       </c>
       <c r="R14" t="n">
-        <v>2.89</v>
+        <v>1.86</v>
       </c>
       <c r="S14" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>2.13</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>3.48</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.55</v>
+        <v>2.46</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.29</v>
+        <v>2.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.88</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61', '90+5']</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '45+1']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46185.58333333334</v>
@@ -2769,26 +2769,26 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '11', '87']</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '84']</t>
         </is>
       </c>
       <c r="AJ15" t="n">
@@ -2871,28 +2871,28 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46185.58333333334</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.51</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>2.59</v>
+        <v>3.15</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.03</v>
+        <v>2.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,16 +3078,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3099,118 +3099,118 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="S17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46185.65625</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,19 +3237,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -3261,42 +3261,42 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.27</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -3305,28 +3305,28 @@
         <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3335,41 +3335,41 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AJ18" t="n">
         <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP18" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46185.65625</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,19 +3396,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3420,115 +3420,115 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="R19" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="U19" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>['85', '87']</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR19" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU19" s="3" t="n">
         <v>46185.65625</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,139 +3555,139 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.4</v>
+        <v>3.58</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.93</v>
+        <v>4.27</v>
       </c>
       <c r="R20" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.37</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AE20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>['14', '18', '34', '71', '89']</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF20" t="n">
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
         <v>2</v>
       </c>
-      <c r="AG20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>-1</v>
-      </c>
       <c r="AN20" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU20" s="3" t="n">
         <v>46185.65625</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,139 +3714,139 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.95</v>
+        <v>1.93</v>
       </c>
       <c r="R21" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="S21" t="n">
         <v>1.37</v>
       </c>
       <c r="T21" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="U21" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>['34', '61']</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AR21" t="n">
         <v>1.05</v>
       </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU21" s="3" t="n">
         <v>46185.65625</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,139 +3873,139 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.06</v>
+        <v>2.51</v>
       </c>
       <c r="R22" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>2.89</v>
       </c>
       <c r="U22" t="n">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
         <v>1.04</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>['26', '67', '72', '74']</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN22" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP22" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU22" s="3" t="n">
         <v>46185.65625</v>
@@ -4041,16 +4041,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '8']</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '34']</t>
         </is>
       </c>
       <c r="AJ23" t="n">
@@ -4143,28 +4143,28 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO23" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP23" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU23" s="3" t="n">
         <v>46185.65625</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,69 +4219,69 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.05</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="AB24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.95</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R25" t="n">
         <v>2.5</v>
       </c>
-      <c r="O25" t="n">
-        <v>3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB25" t="n">
         <v>3.1</v>
       </c>
-      <c r="R25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="AC25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.33</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>

--- a/jogos_2026-06-12.xlsx
+++ b/jogos_2026-06-12.xlsx
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="AA4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.5</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="AS4" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46185.5</v>
@@ -1170,19 +1170,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="O5" t="n">
-        <v>2.44</v>
+        <v>3.04</v>
       </c>
       <c r="P5" t="n">
-        <v>2.91</v>
+        <v>3.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="S5" t="n">
         <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
         <v>2.19</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN5" t="n">
         <v>2</v>
       </c>
-      <c r="AN5" t="n">
-        <v>3</v>
-      </c>
       <c r="AO5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AP5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AT5" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46185.5</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1361,107 +1361,107 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.4</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.12</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.92</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.88</v>
+        <v>6.5</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AK6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.11</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AS6" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AT6" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46185.5</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,31 +1806,31 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
         <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
         <v>1.44</v>
@@ -1868,77 +1868,77 @@
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
         <v>2.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>['37', '41', '54', '90+5']</t>
+          <t>['37', '45+4']</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>['59', '65', '78']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.86</v>
+        <v>1.75</v>
       </c>
       <c r="AS9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AT9" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46185.54166666666</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,31 +1965,31 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1997,28 +1997,28 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
         <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="V10" t="n">
         <v>1.44</v>
@@ -2027,77 +2027,77 @@
         <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB10" t="n">
         <v>2.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['37', '41', '54', '90+5']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>['59', '65', '78']</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>['37', '45+4']</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO10" t="n">
         <v>7</v>
       </c>
-      <c r="AO10" t="n">
-        <v>6</v>
-      </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.79</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.75</v>
+        <v>0.86</v>
       </c>
       <c r="AS10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AT10" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46185.54166666666</v>
@@ -2114,41 +2114,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,107 +2156,107 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>6.25</v>
       </c>
       <c r="P11" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>1.51</v>
       </c>
       <c r="R11" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="S11" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="T11" t="n">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="W11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>['23', '33', '34']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>['57', '74']</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.04</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>['45+3', '67']</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.94</v>
+        <v>4.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN11" t="n">
         <v>4</v>
       </c>
-      <c r="AN11" t="n">
-        <v>6</v>
-      </c>
       <c r="AO11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="AS11" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="AT11" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46185.58333333334</v>
@@ -2273,38 +2273,38 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -2315,107 +2315,107 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.87</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>4.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.78</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="T12" t="n">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="V12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.5</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['45+3', '67']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.28</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.72</v>
+        <v>1.23</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.09</v>
+        <v>1.79</v>
       </c>
       <c r="AS12" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="AT12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46185.58333333334</v>
@@ -2432,149 +2432,149 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>['23', '33', '34']</t>
+          <t>['61', '90+5']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>['57', '74']</t>
+          <t>['20', '45+1']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AK13" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.41</v>
+        <v>0.66</v>
       </c>
       <c r="AS13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AT13" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46185.58333333334</v>
@@ -2591,41 +2591,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2633,107 +2633,107 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.04</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.65</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.13</v>
+        <v>3.12</v>
       </c>
       <c r="U14" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.44</v>
+        <v>1.69</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO14" t="n">
         <v>5</v>
       </c>
-      <c r="AD14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>['61', '90+5']</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>['20', '45+1']</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>9</v>
-      </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.39</v>
+        <v>0.72</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.66</v>
+        <v>1.09</v>
       </c>
       <c r="AS14" t="n">
+        <v>45</v>
+      </c>
+      <c r="AT14" t="n">
         <v>66</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>29</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46185.58333333334</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,22 +3078,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -3110,107 +3110,107 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>['34', '61']</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN17" t="n">
         <v>3</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>7</v>
-      </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.29</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.12</v>
+        <v>1.05</v>
       </c>
       <c r="AS17" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="AT17" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46185.65625</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,31 +3396,31 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -3428,107 +3428,107 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>1.98</v>
       </c>
       <c r="O19" t="n">
         <v>3.3</v>
       </c>
       <c r="P19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>['26', '67', '72', '74']</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>['85', '87']</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO19" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AP19" t="n">
         <v>9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="AS19" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AT19" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AU19" s="3" t="n">
         <v>46185.65625</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,22 +3714,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3746,68 +3746,68 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.93</v>
+        <v>3.06</v>
       </c>
       <c r="R21" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="S21" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.89</v>
+        <v>4.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>['34', '61']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -3816,37 +3816,37 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.9</v>
+        <v>1.49</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AO21" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.29</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.05</v>
+        <v>2.12</v>
       </c>
       <c r="AS21" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="AT21" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="AU21" s="3" t="n">
         <v>46185.65625</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,63 +3873,63 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q22" t="n">
         <v>4</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.51</v>
-      </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T22" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
         <v>1.07</v>
@@ -3938,74 +3938,74 @@
         <v>1.04</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>['4', '8']</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>['11', '34']</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z22" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AK22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
         <v>2</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>['26', '67', '72', '74']</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>7</v>
-      </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO22" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.16</v>
+        <v>1.14</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="AS22" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="AT22" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="AU22" s="3" t="n">
         <v>46185.65625</v>
@@ -4032,139 +4032,139 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>2</v>
       </c>
       <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="U23" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.07</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AF23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>['85', '87']</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z23" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>['4', '8']</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>['11', '34']</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR23" t="n">
         <v>1.19</v>
       </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AS23" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AT23" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AU23" s="3" t="n">
         <v>46185.65625</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R24" t="n">
         <v>2.5</v>
       </c>
-      <c r="O24" t="n">
-        <v>3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB24" t="n">
         <v>3.1</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="AC24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.33</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,69 +4378,69 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.05</v>
       </c>
-      <c r="R25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AB25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.95</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
